--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/OKLAHOMA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/OKLAHOMA_2012.xlsx
@@ -841,7 +841,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="28">
@@ -1363,7 +1363,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="57">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C96">
@@ -2425,7 +2425,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="116">
@@ -2821,7 +2821,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="138">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C146">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C177">
@@ -3559,7 +3559,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="179">
@@ -6511,7 +6511,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="343">
@@ -6907,7 +6907,7 @@
         <v>7</v>
       </c>
       <c r="D364">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="365">
@@ -7177,7 +7177,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="380">
@@ -7465,7 +7465,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="396">
@@ -8815,7 +8815,7 @@
         <v>7</v>
       </c>
       <c r="D470">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="471">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C499">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C560">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C561">
@@ -10633,7 +10633,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="572">
@@ -11965,7 +11965,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="646">
@@ -12631,7 +12631,7 @@
         <v>7</v>
       </c>
       <c r="D682">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="683">
@@ -12955,7 +12955,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="701">
@@ -13621,7 +13621,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="738">
@@ -14557,7 +14557,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="790">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C793">
@@ -15097,7 +15097,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>0.000959956116292</v>
+        <v>0.0009599561162920002</v>
       </c>
     </row>
     <row r="820">
